--- a/03_Group_comparisons/HRvLR/c_data/04_module_contrasts.xlsx
+++ b/03_Group_comparisons/HRvLR/c_data/04_module_contrasts.xlsx
@@ -302,7 +302,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>design</t>
@@ -311,7 +311,7 @@
     <t>03_Group_comparisons/HRvLR/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>2eec838bcc442e8a2ff1534078b14a38</t>
+    <t>49be9910b79653edaceb336779a2265b</t>
   </si>
   <si>
     <t>fit</t>
@@ -320,13 +320,13 @@
     <t>03_Group_comparisons/HRvLR/c_data/02_fit.rds</t>
   </si>
   <si>
-    <t>76d83b782ba641782d378b9ae9391e38</t>
+    <t>97304d26b66df44dfe879e9140989a72</t>
   </si>
   <si>
     <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
   </si>
   <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+    <t>015331bb453caea36bcabbe182b7eac6</t>
   </si>
   <si>
     <t>phenotype</t>
@@ -335,7 +335,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
